--- a/event_registration_forms/042_elderly_assistance_volunteer_application_form--event_registration_forms.xlsx
+++ b/event_registration_forms/042_elderly_assistance_volunteer_application_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -857,8 +857,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,12 +886,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'available',_'label':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Available', 'label': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'unavailable',_'label':_'unavailable'}</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Unavailable', 'label': 'Unavailable'}</t>
+          <t>Unavailable</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'home_visits',_'label':_'home_visits'}</t>
+          <t>home_visits</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Home visits', 'label': 'Home visits'}</t>
+          <t>Home visits</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'telephone_support',_'label':_'telephone_support'}</t>
+          <t>telephone_support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Telephone support', 'label': 'Telephone support'}</t>
+          <t>Telephone support</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'transportation',_'label':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Transportation', 'label': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'meal_delivery',_'label':_'meal_delivery'}</t>
+          <t>meal_delivery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Meal delivery', 'label': 'Meal delivery'}</t>
+          <t>Meal delivery</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'companionship',_'label':_'companionship'}</t>
+          <t>companionship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Companionship', 'label': 'Companionship'}</t>
+          <t>Companionship</t>
         </is>
       </c>
     </row>
